--- a/Benchmark/MeSH_OccO_Gold_Standard.xlsx
+++ b/Benchmark/MeSH_OccO_Gold_Standard.xlsx
@@ -56,6 +56,7 @@
         <sz val="10"/>
         <rFont val="Annapurna SIL"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Food preparation or serving role
 </t>
@@ -65,6 +66,7 @@
         <sz val="10"/>
         <rFont val="Annapurna SIL"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -217,6 +219,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -237,18 +240,21 @@
       <sz val="10"/>
       <name val="Annapurna SIL"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10.5"/>
       <name val="Annapurna SIL"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Annapurna SIL"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -256,6 +262,7 @@
       <color rgb="FF000000"/>
       <name val="Annapurna SIL"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -327,44 +334,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -556,7 +567,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="50.57"/>
@@ -574,10 +585,10 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
+      <c r="E1" s="4"/>
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
@@ -599,140 +610,140 @@
       <c r="G2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="87.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="174.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="102.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="119.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="121.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>14</v>
       </c>
     </row>
